--- a/results/ref_threshold_sensitivity/tables/MaxRel_rda_terms_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/MaxRel_rda_terms_summary.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>110.47</v>
+        <v>154.94</v>
       </c>
       <c r="D2" t="n">
-        <v>4.91</v>
+        <v>6.87</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="3">
@@ -505,24 +505,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>46.83</v>
+        <v>106.74</v>
       </c>
       <c r="D3" t="n">
-        <v>2.08</v>
+        <v>4.73</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>**</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-0.57</v>
+        <v>-0.66</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="4">
@@ -531,28 +531,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.74</v>
+        <v>58.34</v>
       </c>
       <c r="D4" t="n">
-        <v>1.54</v>
+        <v>2.59</v>
       </c>
       <c r="E4" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.58</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5">
@@ -561,17 +561,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.67</v>
+        <v>32.41</v>
       </c>
       <c r="D5" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="H5" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="6">
@@ -591,17 +591,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.4</v>
+        <v>14.17</v>
       </c>
       <c r="D6" t="n">
-        <v>1.26</v>
+        <v>0.63</v>
       </c>
       <c r="E6" t="n">
-        <v>0.23</v>
+        <v>0.71</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>0.62</v>
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>

--- a/results/ref_threshold_sensitivity/tables/MaxRel_rda_terms_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/MaxRel_rda_terms_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/results/ref_threshold_sensitivity/tables/MaxRel_rda_terms_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/MaxRel_rda_terms_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,24 +475,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>154.94</v>
+        <v>50.46</v>
       </c>
       <c r="D2" t="n">
-        <v>6.87</v>
+        <v>2.67</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.41</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +501,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>106.74</v>
+        <v>36.69</v>
       </c>
       <c r="D3" t="n">
-        <v>4.73</v>
+        <v>1.94</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-0.66</v>
+        <v>0.32</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.66</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="4">
@@ -531,28 +531,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58.34</v>
+        <v>32.15</v>
       </c>
       <c r="D4" t="n">
-        <v>2.59</v>
+        <v>1.7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>-0.32</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="5">
@@ -561,17 +561,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.41</v>
+        <v>15.65</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
+        <v>0.83</v>
       </c>
       <c r="E5" t="n">
-        <v>0.16</v>
+        <v>0.55</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-0.44</v>
+        <v>0.12</v>
       </c>
       <c r="H5" t="n">
-        <v>0.48</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -591,17 +591,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14.17</v>
+        <v>11.11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="E6" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-0.01</v>
+        <v>-0.46</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
